--- a/backend/tests/fixtures/phd/خريطة_فرص_الدكتوراه_الشاملة.xlsx
+++ b/backend/tests/fixtures/phd/خريطة_فرص_الدكتوراه_الشاملة.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="لوحة المتابعة" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="كل الفرص" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="سجل التقديمات" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="خطوات قادمة" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تناقضات للتحقق" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الدول" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الملف والمرجعون" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الوثائق والملفات" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="كل الفرص" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="لوحة المتابعة" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="سجل التقديمات" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="خطوات قادمة" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="الدول" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="الملف والمرجعون" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="الوثائق والملفات" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,36 +419,303 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>لوحة متابعة فرص الدكتوراه</t>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>الدولة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المؤسسة / الجامعة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>البرنامج / التخصص</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>المجال الدقيق</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>التمويل</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الموعد النهائي</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظة الموعد</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>الأيام المتبقية</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>حالة الموعد</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>الحالة</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>الأولوية</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>المشرف / جهة الاتصال</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>التحقق</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>تاريخ اليوم</t>
-        </is>
-      </c>
-      <c r="B2">
-        <f>TODAY()</f>
-        <v/>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oxford University</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PhD Computer Science - Prof. Alan Turing Lab</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ممولة بالكامل (Full Scholarship)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>تقديري</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ساري</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>تقديم</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>عالية</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Top candidate program</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Prof. Alan Turing</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>متحقق منه</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>عدد الفرص المسجلة</t>
-        </is>
-      </c>
-      <c r="B3">
-        <f>COUNTA('كل الفرص'!B5:B400)</f>
-        <v/>
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TU Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PhD Informatics</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AI &amp; Cryptography</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ممولة (DAAD Scholarship)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2027-03-01</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>رسمي</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ساري</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>بحث</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>متوسطة</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Strong research lab</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Prof. Ada Lovelace</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>متحقق منه</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PhD Information Security</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Network Defense</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>عقد عمل دكتوراه</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>رسمي</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>160</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ساري</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>بحث</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>عالية</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Security institute</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Prof. John von Neumann</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>متحقق منه</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -463,24 +729,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>خريطة فرص الدكتوراه والتقديمات – أمن سيبراني / أمن الذكاء الاصطناعي</t>
+          <t>إجمالي الفرص</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">أيام الموعد وحالته تُحسب تلقائيًا من تاريخ اليوم. </t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>فرص ممولة</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>طلبات قيد المراجعة</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -492,82 +779,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>التاريخ</t>
+          <t>الرقم</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>البلد</t>
+          <t>الجامعة</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>الجهة / الأستاذ</t>
+          <t>الدولة</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>الإجراء</t>
+          <t>البرنامج</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>الحالة / الخطوة التالية</t>
+          <t>تاريخ التقديم</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الحالة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07-31 00:00:00</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>بلجيكا</t>
+          <t>Oxford University</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KU Leuven – Naessens</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>إرسال قبل الموعد بدقائق</t>
+          <t>PhD Computer Science</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>بانتظار الرد</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>بلجيكا</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>KU Leuven DistriNet – Singelée</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>تقديم على Physical-layer security</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>بانتظار الرد (تاريخ غير مسجل)</t>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>تم التقديم</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Waiting for interview</t>
         </is>
       </c>
     </row>
@@ -582,85 +865,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>التاريخ</t>
+          <t>الخطوة</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>الأيام المتبقية</t>
+          <t>الموعد</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>البلد</t>
+          <t>الفرصة</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>الجهة</t>
+          <t>الحالة</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>المطلوب</t>
+          <t>الأولوية</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="B2">
-        <f>A2-TODAY()</f>
-        <v/>
+          <t>Submit research proposal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>سويسرا</t>
+          <t>Oxford University</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CYD Fellowship</t>
+          <t>مطلوب</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>خطاب الدعم من أستاذ سويسري (فات الموعد؟) – تحقق من</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="B3">
-        <f>A3-TODAY()</f>
-        <v/>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>كندا</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Toronto – Papernot</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>فتح قبول CS PhD Fall 2027 (أكتوبر)</t>
+          <t>عالية</t>
         </is>
       </c>
     </row>
@@ -675,68 +933,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>الدولة</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>الموضوع</t>
+          <t>عدد الفرص</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>ما تقوله المصادر</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>المطلوب</t>
+          <t>ملاحظات</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>لوكسمبورغ/SnT – Lenders</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>UOL07942 هو نفسه المنصب المستبعد 15.08 (غير مؤهل).</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>اعرف أي منصب قدّمت عليه فعلاً، وتحقق من أهلية 2435</t>
+          <t>Top tier universities</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>كندا/UNB – Dadkhah</t>
-        </is>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16.08: أولوية عليا بإعلان Fully Funded MSc/PhD. 23</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>افتح الإعلان الأصلي وتحقق.</t>
+          <t>Excellent research facilities</t>
         </is>
       </c>
     </row>
@@ -751,60 +994,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>الدولة</t>
+          <t>الاسم الكامل</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>عدد الصفوف</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>صفوف تم التقديم/التواصل فيها</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ملاحظة</t>
+          <t>Abdallah Benaicha</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>إيطاليا</t>
-        </is>
-      </c>
-      <c r="B2">
-        <f>COUNTIF('كل الفرص'!$B$5:$B$400,A2)</f>
-        <v/>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>+1234567890</t>
+          <t>الدرجة الحالية</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Master in Cybersecurity (ماجستير)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>سويسرا</t>
-        </is>
-      </c>
-      <c r="B3">
-        <f>COUNTIF('كل الفرص'!$B$5:$B$400,A3)</f>
-        <v/>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>+1234567890</t>
+          <t>المجال</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Offensive Security &amp; Red Teaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>البريد الإلكتروني</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>candidate@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>جهات المرجع</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dr. Test Reference</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ref1@example.edu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Academic Supervisor</t>
         </is>
       </c>
     </row>
@@ -819,102 +1080,74 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>الملف الأكاديمي</t>
+          <t>اسم الوثيقة</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>الجهة المستهدفة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحالة</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>التخصص</t>
+          <t>Academic_CV.pdf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Network Information Communication Technologies (NI</t>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>جاهز</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>الجامعة</t>
+          <t>Research_Proposal.pdf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>جامعة محمد بوضياف – المسيلة، دفعة 2024-2026</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>الملف / الوثيقة</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>الجهة المستهدفة</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>الحالة</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>research_proposal.md</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>عام</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>جاهز</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>cispa_research_statement.md</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CISPA – Ali Abbasi</t>
+          <t>Oxford University</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>جاهز / أُرسل</t>
+          <t>مسودة</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Transcripts.pdf</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>مترجم ومصدق</t>
         </is>
       </c>
     </row>
